--- a/input/Domains/Sound/SoundTable.xlsx
+++ b/input/Domains/Sound/SoundTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Devwinsoft\devian\input\Domains\Sound\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Sound/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64088142-E93D-4AC2-BC49-965960660A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C31203-75F6-C447-8452-C5F7E395A4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="900" windowWidth="25635" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="900" windowWidth="25640" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOUND" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,9 +527,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -623,7 +627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -631,12 +635,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15">
       <c r="F4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>1</v>
       </c>
@@ -683,7 +687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>2</v>
       </c>
@@ -730,7 +734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>3</v>
       </c>
@@ -777,7 +781,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>4</v>
       </c>
@@ -824,7 +828,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>5</v>
       </c>
@@ -871,7 +875,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>6</v>
       </c>
@@ -918,7 +922,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>7</v>
       </c>
@@ -974,12 +978,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1020,7 +1024,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1061,12 +1065,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1104,7 +1108,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>45</v>
       </c>
